--- a/Übungen/03_Netzplan_CMS.xlsx
+++ b/Übungen/03_Netzplan_CMS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
   <si>
     <t xml:space="preserve">Projekt:</t>
   </si>
@@ -246,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="13">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -338,41 +338,6 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thick"/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick"/>
-      <right/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thick"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -402,7 +367,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -539,28 +504,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -685,8 +630,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG50"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB50"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="2" style="0" width="3.83"/>
@@ -1029,24 +974,6 @@
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="31"/>
-      <c r="AG13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
@@ -1054,36 +981,6 @@
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
-      <c r="F14" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="K14" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="P14" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="U14" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="V14" s="32"/>
-      <c r="W14" s="32"/>
-      <c r="Z14" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA14" s="32"/>
-      <c r="AB14" s="32"/>
-      <c r="AE14" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF14" s="32"/>
-      <c r="AG14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="n">
@@ -1091,149 +988,13 @@
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="32"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="32"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="32"/>
-      <c r="AG15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="n">
+      <c r="A16" s="34" t="n">
         <v>0</v>
       </c>
       <c r="B16" s="29"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="37"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="37"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="29"/>
-      <c r="AG16" s="37"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="38"/>
-      <c r="J17" s="39"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="38"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="30"/>
-      <c r="J18" s="39"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="38"/>
-      <c r="F19" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="J19" s="39"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="38"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="39"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="38"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="37"/>
-      <c r="J21" s="39"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="38"/>
-      <c r="J22" s="39"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="38"/>
-      <c r="F23" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="30"/>
-      <c r="J23" s="39"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="38"/>
-      <c r="F24" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="J24" s="39"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="35"/>
-      <c r="F25" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="35"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="37"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="37"/>
+      <c r="C16" s="34"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0"/>
@@ -1242,214 +1003,214 @@
       <c r="A31" s="0"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="40"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="41"/>
+      <c r="L38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="40"/>
-      <c r="B39" s="42" t="s">
+      <c r="A39" s="35"/>
+      <c r="B39" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="F39" s="43" t="s">
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="F39" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="L39" s="41"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="L39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="40"/>
-      <c r="B40" s="44" t="s">
+      <c r="A40" s="35"/>
+      <c r="B40" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="45" t="s">
+      <c r="C40" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="44" t="s">
+      <c r="D40" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="41"/>
+      <c r="L40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="40"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="0" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="L41" s="41"/>
+      <c r="L41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="40"/>
-      <c r="L42" s="41"/>
+      <c r="A42" s="35"/>
+      <c r="L42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="40"/>
-      <c r="B43" s="46" t="s">
+      <c r="A43" s="35"/>
+      <c r="B43" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="47" t="s">
+      <c r="C43" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="40"/>
-      <c r="B44" s="46" t="s">
+      <c r="A44" s="35"/>
+      <c r="B44" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="47" t="s">
+      <c r="C44" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="40"/>
-      <c r="B45" s="46" t="s">
+      <c r="A45" s="35"/>
+      <c r="B45" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="47" t="s">
+      <c r="C45" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="41"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="40"/>
-      <c r="B46" s="46" t="s">
+      <c r="A46" s="35"/>
+      <c r="B46" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="47" t="s">
+      <c r="C46" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="41"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="40"/>
-      <c r="B47" s="44" t="s">
+      <c r="A47" s="35"/>
+      <c r="B47" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
-      <c r="L47" s="41"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="40"/>
-      <c r="B48" s="45" t="s">
+      <c r="A48" s="35"/>
+      <c r="B48" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
-      <c r="L48" s="41"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="40"/>
-      <c r="B49" s="48" t="s">
+      <c r="A49" s="35"/>
+      <c r="B49" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="41" t="s">
+      <c r="C49" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="40"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="24">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:P1"/>
     <mergeCell ref="Q1:AB1"/>
@@ -1466,14 +1227,6 @@
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AE14:AG14"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F39:J39"/>
     <mergeCell ref="C43:K43"/>
@@ -1483,7 +1236,7 @@
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C48:K48"/>
   </mergeCells>
-  <conditionalFormatting sqref="G15 G20 G25 L15 Q15 V15 AA15 AF15 B15">
+  <conditionalFormatting sqref="B15">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/03_Netzplan_CMS.xlsx
+++ b/Übungen/03_Netzplan_CMS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t xml:space="preserve">Projekt:</t>
   </si>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">Seitenstruktur erstellen</t>
   </si>
   <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fotos / Grafiken erstellen</t>
   </si>
   <si>
@@ -76,13 +79,10 @@
     <t xml:space="preserve">Tests / Korrekturen</t>
   </si>
   <si>
-    <t xml:space="preserve">G</t>
+    <t xml:space="preserve">H</t>
   </si>
   <si>
     <t xml:space="preserve">Kundenpräsentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H</t>
   </si>
   <si>
     <t xml:space="preserve">Eventuelle Anpassungen</t>
@@ -140,10 +140,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -194,6 +195,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Alegreya Sans"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
@@ -214,7 +221,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +232,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
         <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -338,6 +351,41 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -367,7 +415,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -400,6 +448,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -408,15 +460,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -430,6 +482,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -468,71 +532,95 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -540,7 +628,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -554,12 +642,24 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="GP" xfId="20"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="1"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDDDDD"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -580,7 +680,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
@@ -630,8 +730,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB50"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BL50"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="2" style="0" width="3.83"/>
@@ -671,7 +771,7 @@
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="42.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -699,302 +799,1092 @@
       <c r="Q2" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="R2" s="8" t="n">
+        <v>44606</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>44607</v>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v>44608</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>44609</v>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v>44610</v>
+      </c>
+      <c r="W2" s="8" t="n">
+        <v>44611</v>
+      </c>
+      <c r="X2" s="8" t="n">
+        <v>44612</v>
+      </c>
+      <c r="Y2" s="8" t="n">
+        <v>44613</v>
+      </c>
+      <c r="Z2" s="8" t="n">
+        <v>44614</v>
+      </c>
+      <c r="AA2" s="8" t="n">
+        <v>44615</v>
+      </c>
+      <c r="AB2" s="8" t="n">
+        <v>44616</v>
+      </c>
+      <c r="AC2" s="8" t="n">
+        <v>44617</v>
+      </c>
+      <c r="AD2" s="8" t="n">
+        <v>44618</v>
+      </c>
+      <c r="AE2" s="8" t="n">
+        <v>44619</v>
+      </c>
+      <c r="AF2" s="8" t="n">
+        <v>44620</v>
+      </c>
+      <c r="AG2" s="8" t="n">
+        <v>44621</v>
+      </c>
+      <c r="AH2" s="8" t="n">
+        <v>44622</v>
+      </c>
+      <c r="AI2" s="8" t="n">
+        <v>44623</v>
+      </c>
+      <c r="AJ2" s="8" t="n">
+        <v>44624</v>
+      </c>
+      <c r="AK2" s="8" t="n">
+        <v>44625</v>
+      </c>
+      <c r="AL2" s="8" t="n">
+        <v>44626</v>
+      </c>
+      <c r="AM2" s="8" t="n">
+        <v>44627</v>
+      </c>
+      <c r="AN2" s="8" t="n">
+        <v>44628</v>
+      </c>
+      <c r="AO2" s="8" t="n">
+        <v>44629</v>
+      </c>
+      <c r="AP2" s="8" t="n">
+        <v>44630</v>
+      </c>
+      <c r="AQ2" s="8" t="n">
+        <v>44631</v>
+      </c>
+      <c r="AR2" s="8" t="n">
+        <v>44632</v>
+      </c>
+      <c r="AS2" s="8" t="n">
+        <v>44633</v>
+      </c>
+      <c r="AT2" s="8" t="n">
+        <v>44634</v>
+      </c>
+      <c r="AU2" s="8" t="n">
+        <v>44635</v>
+      </c>
+      <c r="AV2" s="8" t="n">
+        <v>44636</v>
+      </c>
+      <c r="AW2" s="8" t="n">
+        <v>44637</v>
+      </c>
+      <c r="AX2" s="8" t="n">
+        <v>44638</v>
+      </c>
+      <c r="AY2" s="8" t="n">
+        <v>44639</v>
+      </c>
+      <c r="AZ2" s="8" t="n">
+        <v>44640</v>
+      </c>
+      <c r="BA2" s="8" t="n">
+        <v>44641</v>
+      </c>
+      <c r="BB2" s="8" t="n">
+        <v>44642</v>
+      </c>
+      <c r="BC2" s="8" t="n">
+        <v>44643</v>
+      </c>
+      <c r="BD2" s="8" t="n">
+        <v>44644</v>
+      </c>
+      <c r="BE2" s="8" t="n">
+        <v>44645</v>
+      </c>
+      <c r="BF2" s="8" t="n">
+        <v>44646</v>
+      </c>
+      <c r="BG2" s="8" t="n">
+        <v>44647</v>
+      </c>
+      <c r="BH2" s="8" t="n">
+        <v>44648</v>
+      </c>
+      <c r="BI2" s="8" t="n">
+        <v>44649</v>
+      </c>
+      <c r="BJ2" s="8" t="n">
+        <v>44650</v>
+      </c>
+      <c r="BK2" s="8" t="n">
+        <v>44651</v>
+      </c>
+      <c r="BL2" s="8" t="n">
+        <v>44652</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="8" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="15" t="n">
+      <c r="P3" s="15"/>
+      <c r="Q3" s="16" t="n">
         <v>1</v>
       </c>
+      <c r="R3" s="17"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="17"/>
+      <c r="AM3" s="18"/>
+      <c r="AN3" s="18"/>
+      <c r="AO3" s="18"/>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="18"/>
+      <c r="AS3" s="18"/>
+      <c r="AT3" s="18"/>
+      <c r="AU3" s="18"/>
+      <c r="AV3" s="18"/>
+      <c r="AW3" s="18"/>
+      <c r="AX3" s="18"/>
+      <c r="AY3" s="18"/>
+      <c r="AZ3" s="18"/>
+      <c r="BA3" s="18"/>
+      <c r="BB3" s="18"/>
+      <c r="BC3" s="18"/>
+      <c r="BD3" s="18"/>
+      <c r="BE3" s="18"/>
+      <c r="BF3" s="18"/>
+      <c r="BG3" s="18"/>
+      <c r="BH3" s="18"/>
+      <c r="BI3" s="18"/>
+      <c r="BJ3" s="18"/>
+      <c r="BK3" s="18"/>
+      <c r="BL3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="16" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="16" t="s">
+      <c r="L4" s="22"/>
+      <c r="M4" s="20" t="s">
         <v>12</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="19" t="n">
+      <c r="P4" s="22"/>
+      <c r="Q4" s="23" t="n">
         <v>2</v>
       </c>
+      <c r="R4" s="17"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="17"/>
+      <c r="AI4" s="17"/>
+      <c r="AJ4" s="17"/>
+      <c r="AK4" s="17"/>
+      <c r="AL4" s="17"/>
+      <c r="AM4" s="18"/>
+      <c r="AN4" s="18"/>
+      <c r="AO4" s="18"/>
+      <c r="AP4" s="18"/>
+      <c r="AQ4" s="18"/>
+      <c r="AR4" s="18"/>
+      <c r="AS4" s="18"/>
+      <c r="AT4" s="18"/>
+      <c r="AU4" s="18"/>
+      <c r="AV4" s="18"/>
+      <c r="AW4" s="18"/>
+      <c r="AX4" s="18"/>
+      <c r="AY4" s="18"/>
+      <c r="AZ4" s="18"/>
+      <c r="BA4" s="18"/>
+      <c r="BB4" s="18"/>
+      <c r="BC4" s="18"/>
+      <c r="BD4" s="18"/>
+      <c r="BE4" s="18"/>
+      <c r="BF4" s="18"/>
+      <c r="BG4" s="18"/>
+      <c r="BH4" s="18"/>
+      <c r="BI4" s="18"/>
+      <c r="BJ4" s="18"/>
+      <c r="BK4" s="18"/>
+      <c r="BL4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="16" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="20" t="s">
         <v>7</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="16" t="s">
-        <v>12</v>
+      <c r="L5" s="22"/>
+      <c r="M5" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="19" t="n">
+      <c r="P5" s="22"/>
+      <c r="Q5" s="23" t="n">
         <v>2</v>
       </c>
+      <c r="R5" s="17"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="17"/>
+      <c r="AG5" s="17"/>
+      <c r="AH5" s="17"/>
+      <c r="AI5" s="17"/>
+      <c r="AJ5" s="17"/>
+      <c r="AK5" s="17"/>
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="18"/>
+      <c r="AN5" s="18"/>
+      <c r="AO5" s="18"/>
+      <c r="AP5" s="18"/>
+      <c r="AQ5" s="18"/>
+      <c r="AR5" s="18"/>
+      <c r="AS5" s="18"/>
+      <c r="AT5" s="18"/>
+      <c r="AU5" s="18"/>
+      <c r="AV5" s="18"/>
+      <c r="AW5" s="18"/>
+      <c r="AX5" s="18"/>
+      <c r="AY5" s="18"/>
+      <c r="AZ5" s="18"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="18"/>
+      <c r="BD5" s="18"/>
+      <c r="BE5" s="18"/>
+      <c r="BF5" s="18"/>
+      <c r="BG5" s="18"/>
+      <c r="BH5" s="18"/>
+      <c r="BI5" s="18"/>
+      <c r="BJ5" s="18"/>
+      <c r="BK5" s="18"/>
+      <c r="BL5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="16" t="s">
+      <c r="B6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="20" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="16" t="s">
-        <v>12</v>
+      <c r="L6" s="22"/>
+      <c r="M6" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="19" t="n">
+      <c r="P6" s="22"/>
+      <c r="Q6" s="23" t="n">
         <v>5</v>
       </c>
+      <c r="R6" s="17"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="17"/>
+      <c r="AI6" s="17"/>
+      <c r="AJ6" s="17"/>
+      <c r="AK6" s="17"/>
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="18"/>
+      <c r="AN6" s="18"/>
+      <c r="AO6" s="18"/>
+      <c r="AP6" s="18"/>
+      <c r="AQ6" s="18"/>
+      <c r="AR6" s="18"/>
+      <c r="AS6" s="18"/>
+      <c r="AT6" s="18"/>
+      <c r="AU6" s="18"/>
+      <c r="AV6" s="18"/>
+      <c r="AW6" s="18"/>
+      <c r="AX6" s="18"/>
+      <c r="AY6" s="18"/>
+      <c r="AZ6" s="18"/>
+      <c r="BA6" s="18"/>
+      <c r="BB6" s="18"/>
+      <c r="BC6" s="18"/>
+      <c r="BD6" s="18"/>
+      <c r="BE6" s="18"/>
+      <c r="BF6" s="18"/>
+      <c r="BG6" s="18"/>
+      <c r="BH6" s="18"/>
+      <c r="BI6" s="18"/>
+      <c r="BJ6" s="18"/>
+      <c r="BK6" s="18"/>
+      <c r="BL6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="16" t="s">
+      <c r="B7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="18"/>
-      <c r="M7" s="16" t="s">
-        <v>16</v>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="20" t="s">
+        <v>17</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="19" t="n">
+      <c r="P7" s="22"/>
+      <c r="Q7" s="23" t="n">
         <v>2</v>
       </c>
+      <c r="R7" s="17"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="17"/>
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="18"/>
+      <c r="AN7" s="18"/>
+      <c r="AO7" s="18"/>
+      <c r="AP7" s="18"/>
+      <c r="AQ7" s="18"/>
+      <c r="AR7" s="18"/>
+      <c r="AS7" s="18"/>
+      <c r="AT7" s="18"/>
+      <c r="AU7" s="18"/>
+      <c r="AV7" s="18"/>
+      <c r="AW7" s="18"/>
+      <c r="AX7" s="18"/>
+      <c r="AY7" s="18"/>
+      <c r="AZ7" s="18"/>
+      <c r="BA7" s="18"/>
+      <c r="BB7" s="18"/>
+      <c r="BC7" s="18"/>
+      <c r="BD7" s="18"/>
+      <c r="BE7" s="18"/>
+      <c r="BF7" s="18"/>
+      <c r="BG7" s="18"/>
+      <c r="BH7" s="18"/>
+      <c r="BI7" s="18"/>
+      <c r="BJ7" s="18"/>
+      <c r="BK7" s="18"/>
+      <c r="BL7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="16" t="s">
+      <c r="B8" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="20" t="s">
         <v>12</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="16" t="s">
-        <v>18</v>
+      <c r="L8" s="22"/>
+      <c r="M8" s="20" t="s">
+        <v>19</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="19" t="n">
+      <c r="P8" s="22"/>
+      <c r="Q8" s="23" t="n">
         <v>3</v>
       </c>
+      <c r="R8" s="17"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="18"/>
+      <c r="AN8" s="18"/>
+      <c r="AO8" s="18"/>
+      <c r="AP8" s="18"/>
+      <c r="AQ8" s="18"/>
+      <c r="AR8" s="18"/>
+      <c r="AS8" s="18"/>
+      <c r="AT8" s="18"/>
+      <c r="AU8" s="18"/>
+      <c r="AV8" s="18"/>
+      <c r="AW8" s="18"/>
+      <c r="AX8" s="18"/>
+      <c r="AY8" s="18"/>
+      <c r="AZ8" s="18"/>
+      <c r="BA8" s="18"/>
+      <c r="BB8" s="18"/>
+      <c r="BC8" s="18"/>
+      <c r="BD8" s="18"/>
+      <c r="BE8" s="18"/>
+      <c r="BF8" s="18"/>
+      <c r="BG8" s="18"/>
+      <c r="BH8" s="18"/>
+      <c r="BI8" s="18"/>
+      <c r="BJ8" s="18"/>
+      <c r="BK8" s="18"/>
+      <c r="BL8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="20" t="s">
         <v>19</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="19" t="n">
+      <c r="P9" s="22"/>
+      <c r="Q9" s="23" t="n">
         <v>1</v>
       </c>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="17"/>
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="17"/>
+      <c r="AQ9" s="17"/>
+      <c r="AR9" s="17"/>
+      <c r="AS9" s="17"/>
+      <c r="AT9" s="17"/>
+      <c r="AU9" s="17"/>
+      <c r="AV9" s="17"/>
+      <c r="AW9" s="17"/>
+      <c r="AX9" s="17"/>
+      <c r="AY9" s="17"/>
+      <c r="AZ9" s="17"/>
+      <c r="BA9" s="17"/>
+      <c r="BB9" s="17"/>
+      <c r="BC9" s="17"/>
+      <c r="BD9" s="17"/>
+      <c r="BE9" s="17"/>
+      <c r="BF9" s="17"/>
+      <c r="BG9" s="17"/>
+      <c r="BH9" s="17"/>
+      <c r="BI9" s="17"/>
+      <c r="BJ9" s="17"/>
+      <c r="BK9" s="17"/>
+      <c r="BL9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="1"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="16" t="s">
+      <c r="L10" s="22"/>
+      <c r="M10" s="20" t="s">
         <v>22</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="19" t="n">
+      <c r="P10" s="22"/>
+      <c r="Q10" s="23" t="n">
         <v>3</v>
       </c>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="17"/>
+      <c r="AN10" s="17"/>
+      <c r="AO10" s="17"/>
+      <c r="AP10" s="17"/>
+      <c r="AQ10" s="17"/>
+      <c r="AR10" s="17"/>
+      <c r="AS10" s="17"/>
+      <c r="AT10" s="17"/>
+      <c r="AU10" s="17"/>
+      <c r="AV10" s="17"/>
+      <c r="AW10" s="17"/>
+      <c r="AX10" s="17"/>
+      <c r="AY10" s="17"/>
+      <c r="AZ10" s="17"/>
+      <c r="BA10" s="17"/>
+      <c r="BB10" s="17"/>
+      <c r="BC10" s="17"/>
+      <c r="BD10" s="17"/>
+      <c r="BE10" s="17"/>
+      <c r="BF10" s="17"/>
+      <c r="BG10" s="17"/>
+      <c r="BH10" s="17"/>
+      <c r="BI10" s="17"/>
+      <c r="BJ10" s="17"/>
+      <c r="BK10" s="17"/>
+      <c r="BL10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="28" t="n">
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="32" t="n">
         <v>1</v>
       </c>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="33"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="33"/>
+      <c r="AO11" s="33"/>
+      <c r="AP11" s="33"/>
+      <c r="AQ11" s="33"/>
+      <c r="AR11" s="33"/>
+      <c r="AS11" s="33"/>
+      <c r="AT11" s="33"/>
+      <c r="AU11" s="33"/>
+      <c r="AV11" s="33"/>
+      <c r="AW11" s="33"/>
+      <c r="AX11" s="33"/>
+      <c r="AY11" s="33"/>
+      <c r="AZ11" s="33"/>
+      <c r="BA11" s="33"/>
+      <c r="BB11" s="33"/>
+      <c r="BC11" s="33"/>
+      <c r="BD11" s="33"/>
+      <c r="BE11" s="33"/>
+      <c r="BF11" s="33"/>
+      <c r="BG11" s="33"/>
+      <c r="BH11" s="33"/>
+      <c r="BI11" s="33"/>
+      <c r="BJ11" s="33"/>
+      <c r="BK11" s="33"/>
+      <c r="BL11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29"/>
+      <c r="B12" s="34"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="30"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="35"/>
+      <c r="F13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="36"/>
+      <c r="H13" s="35"/>
+      <c r="K13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="36"/>
+      <c r="M13" s="35"/>
+      <c r="P13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="35"/>
+      <c r="U13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="36"/>
+      <c r="W13" s="35"/>
+      <c r="Z13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="F14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="K14" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="P14" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="U14" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="Z14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA14" s="37"/>
+      <c r="AB14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="n">
+      <c r="A15" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="37"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="37"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="37"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="37"/>
+      <c r="AB15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="n">
+      <c r="A16" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
+      <c r="F16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="34"/>
+      <c r="H16" s="42"/>
+      <c r="K16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="34"/>
+      <c r="M16" s="42"/>
+      <c r="P16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="42"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="34"/>
+      <c r="W16" s="42"/>
+      <c r="Z16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="42"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="43"/>
+      <c r="T17" s="44"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="43"/>
+      <c r="T18" s="44"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="43"/>
+      <c r="F19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="36"/>
+      <c r="H19" s="35"/>
+      <c r="P19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="35"/>
+      <c r="T19" s="44"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="43"/>
+      <c r="F20" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="P20" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="T20" s="44"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="43"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="40"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="43"/>
+      <c r="F22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="34"/>
+      <c r="H22" s="42"/>
+      <c r="J22" s="44"/>
+      <c r="P22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="42"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="43"/>
+      <c r="J23" s="44"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24" s="43"/>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D25" s="43"/>
+      <c r="F25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="36"/>
+      <c r="H25" s="35"/>
+      <c r="J25" s="44"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="43"/>
+      <c r="F26" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="J26" s="44"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="40"/>
+      <c r="F27" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="40"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F28" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="34"/>
+      <c r="H28" s="42"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0"/>
@@ -1003,214 +1893,214 @@
       <c r="A31" s="0"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="35"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="36"/>
+      <c r="A37" s="45"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="46"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="35"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="36"/>
+      <c r="L38" s="46"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="35"/>
-      <c r="B39" s="37" t="s">
+      <c r="A39" s="45"/>
+      <c r="B39" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="F39" s="38" t="s">
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="F39" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="L39" s="36"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="L39" s="46"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="35"/>
-      <c r="B40" s="39" t="s">
+      <c r="A40" s="45"/>
+      <c r="B40" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="36"/>
+      <c r="L40" s="46"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="35"/>
+      <c r="A41" s="45"/>
       <c r="B41" s="0" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="L41" s="36"/>
+      <c r="L41" s="46"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="35"/>
-      <c r="L42" s="36"/>
+      <c r="A42" s="45"/>
+      <c r="L42" s="46"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="35"/>
-      <c r="B43" s="41" t="s">
+      <c r="A43" s="45"/>
+      <c r="B43" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
-      <c r="K43" s="42"/>
-      <c r="L43" s="36"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="46"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="35"/>
-      <c r="B44" s="41" t="s">
+      <c r="A44" s="45"/>
+      <c r="B44" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
-      <c r="K44" s="42"/>
-      <c r="L44" s="36"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="46"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="35"/>
-      <c r="B45" s="41" t="s">
+      <c r="A45" s="45"/>
+      <c r="B45" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="36"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="46"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="35"/>
-      <c r="B46" s="41" t="s">
+      <c r="A46" s="45"/>
+      <c r="B46" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
-      <c r="K46" s="42"/>
-      <c r="L46" s="36"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="46"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="35"/>
-      <c r="B47" s="39" t="s">
+      <c r="A47" s="45"/>
+      <c r="B47" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="36"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="46"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="35"/>
-      <c r="B48" s="40" t="s">
+      <c r="A48" s="45"/>
+      <c r="B48" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
-      <c r="K48" s="42"/>
-      <c r="L48" s="36"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="46"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="35"/>
-      <c r="B49" s="43" t="s">
+      <c r="A49" s="45"/>
+      <c r="B49" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="36"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="35"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="36"/>
-      <c r="L50" s="36"/>
+      <c r="A50" s="45"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="46"/>
+      <c r="L50" s="46"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="32">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:P1"/>
     <mergeCell ref="Q1:AB1"/>
@@ -1227,6 +2117,14 @@
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F39:J39"/>
     <mergeCell ref="C43:K43"/>
@@ -1236,9 +2134,14 @@
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C48:K48"/>
   </mergeCells>
-  <conditionalFormatting sqref="B15">
+  <conditionalFormatting sqref="B15 G15 G21 G27 L15 Q15 Q21 V15 AA15">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:BL11">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>IF(OR(WEEKDAY(R$2,2)=6,WEEKDAY(R$2,2)=7),1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Übungen/03_Netzplan_CMS.xlsx
+++ b/Übungen/03_Netzplan_CMS.xlsx
@@ -464,7 +464,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="71">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -521,7 +521,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -533,10 +533,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -627,22 +623,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -782,12 +762,6 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <b val="1"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <name val="Arial"/>
         <charset val="1"/>
         <family val="2"/>
@@ -797,6 +771,12 @@
           <bgColor rgb="FFDDDDDD"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
   </dxfs>
   <colors>
@@ -873,9 +853,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>185040</xdr:colOff>
+      <xdr:colOff>184680</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -885,7 +865,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4683960" y="846360"/>
-          <a:ext cx="99720" cy="128880"/>
+          <a:ext cx="99360" cy="128520"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -940,9 +920,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>171360</xdr:colOff>
+      <xdr:colOff>171000</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>140760</xdr:rowOff>
+      <xdr:rowOff>140400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -952,7 +932,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7104600" y="2001240"/>
-          <a:ext cx="99720" cy="128880"/>
+          <a:ext cx="99360" cy="128520"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -1007,9 +987,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>171360</xdr:colOff>
+      <xdr:colOff>171000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>120960</xdr:rowOff>
+      <xdr:rowOff>120600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1019,7 +999,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8727840" y="2468880"/>
-          <a:ext cx="99720" cy="128880"/>
+          <a:ext cx="99360" cy="128520"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -1073,8 +1053,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ52"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AL52"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="2" style="0" width="3.83"/>
@@ -1206,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" s="17" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
@@ -1243,89 +1223,57 @@
       <c r="AF3" s="16"/>
       <c r="AG3" s="16"/>
       <c r="AH3" s="16"/>
-      <c r="AI3" s="0"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="12"/>
       <c r="AL3" s="13"/>
-      <c r="AM3" s="0"/>
-      <c r="AN3" s="0"/>
-      <c r="AO3" s="0"/>
-      <c r="AP3" s="0"/>
-      <c r="AQ3" s="0"/>
-      <c r="AR3" s="0"/>
-      <c r="AS3" s="0"/>
-      <c r="AT3" s="0"/>
-      <c r="AU3" s="0"/>
-      <c r="AV3" s="0"/>
-      <c r="AW3" s="0"/>
-      <c r="AX3" s="0"/>
-      <c r="AY3" s="0"/>
-      <c r="AZ3" s="0"/>
-      <c r="BA3" s="0"/>
-      <c r="BB3" s="0"/>
-      <c r="BC3" s="0"/>
-      <c r="BD3" s="0"/>
-      <c r="BE3" s="0"/>
-      <c r="BF3" s="0"/>
-      <c r="BG3" s="0"/>
-      <c r="BH3" s="0"/>
-      <c r="BI3" s="0"/>
-      <c r="BJ3" s="0"/>
-      <c r="BK3" s="0"/>
-      <c r="BL3" s="0"/>
-      <c r="BM3" s="0"/>
-      <c r="BN3" s="0"/>
-      <c r="BO3" s="0"/>
-      <c r="BP3" s="0"/>
-      <c r="BQ3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="18" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="23" t="s">
+      <c r="N4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="25" t="n">
+      <c r="P4" s="23"/>
+      <c r="Q4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="26"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
       <c r="AJ4" s="11" t="s">
         <v>15</v>
       </c>
@@ -1333,50 +1281,50 @@
       <c r="AL4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="30" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="30" t="s">
+      <c r="L5" s="31"/>
+      <c r="M5" s="29" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="33" t="n">
+      <c r="P5" s="31"/>
+      <c r="Q5" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R5" s="29"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
       <c r="AJ5" s="11" t="s">
         <v>15</v>
       </c>
@@ -1384,50 +1332,50 @@
       <c r="AL5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="30" t="s">
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="30" t="s">
+      <c r="L6" s="31"/>
+      <c r="M6" s="29" t="s">
         <v>19</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="33" t="n">
+      <c r="P6" s="31"/>
+      <c r="Q6" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R6" s="29"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
       <c r="AJ6" s="11"/>
       <c r="AK6" s="12" t="s">
         <v>15</v>
@@ -1437,50 +1385,50 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="30" t="s">
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="29" t="s">
         <v>11</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="30" t="s">
+      <c r="L7" s="31"/>
+      <c r="M7" s="29" t="s">
         <v>19</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="33" t="n">
+      <c r="P7" s="31"/>
+      <c r="Q7" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="29"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
       <c r="AJ7" s="11"/>
       <c r="AK7" s="12" t="s">
         <v>15</v>
@@ -1488,50 +1436,50 @@
       <c r="AL7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="30" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="29" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="30" t="s">
+      <c r="L8" s="31"/>
+      <c r="M8" s="29" t="s">
         <v>22</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="33" t="n">
+      <c r="P8" s="31"/>
+      <c r="Q8" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="R8" s="29"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="29"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
       <c r="AJ8" s="11" t="s">
         <v>15</v>
       </c>
@@ -1539,175 +1487,143 @@
       <c r="AL8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="30" t="s">
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="29" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="30" t="s">
+      <c r="L9" s="31"/>
+      <c r="M9" s="29" t="s">
         <v>24</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="33" t="n">
+      <c r="P9" s="31"/>
+      <c r="Q9" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="R9" s="29"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
       <c r="AJ9" s="11"/>
       <c r="AK9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="AL9" s="13"/>
     </row>
-    <row r="10" s="17" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="s">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="42"/>
-      <c r="AA10" s="42"/>
-      <c r="AB10" s="42"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="42"/>
-      <c r="AE10" s="42"/>
-      <c r="AF10" s="42"/>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="42"/>
-      <c r="AI10" s="0"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="28"/>
+      <c r="AH10" s="28"/>
       <c r="AJ10" s="11"/>
       <c r="AK10" s="12"/>
       <c r="AL10" s="13"/>
-      <c r="AM10" s="0"/>
-      <c r="AN10" s="0"/>
-      <c r="AO10" s="0"/>
-      <c r="AP10" s="0"/>
-      <c r="AQ10" s="0"/>
-      <c r="AR10" s="0"/>
-      <c r="AS10" s="0"/>
-      <c r="AT10" s="0"/>
-      <c r="AU10" s="0"/>
-      <c r="AV10" s="0"/>
-      <c r="AW10" s="0"/>
-      <c r="AX10" s="0"/>
-      <c r="AY10" s="0"/>
-      <c r="AZ10" s="0"/>
-      <c r="BA10" s="0"/>
-      <c r="BB10" s="0"/>
-      <c r="BC10" s="0"/>
-      <c r="BD10" s="0"/>
-      <c r="BE10" s="0"/>
-      <c r="BF10" s="0"/>
-      <c r="BG10" s="0"/>
-      <c r="BH10" s="0"/>
-      <c r="BI10" s="0"/>
-      <c r="BJ10" s="0"/>
-      <c r="BK10" s="0"/>
-      <c r="BL10" s="0"/>
-      <c r="BM10" s="0"/>
-      <c r="BN10" s="0"/>
-      <c r="BO10" s="0"/>
-      <c r="BP10" s="0"/>
-      <c r="BQ10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="30" t="s">
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="29" t="s">
         <v>14</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="30" t="s">
+      <c r="L11" s="31"/>
+      <c r="M11" s="29" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="33" t="n">
+      <c r="P11" s="31"/>
+      <c r="Q11" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="AA11" s="38"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="28"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="28"/>
+      <c r="AH11" s="28"/>
       <c r="AJ11" s="11"/>
       <c r="AK11" s="12"/>
       <c r="AL11" s="13" t="s">
@@ -1715,52 +1631,52 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="30" t="s">
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="29" t="s">
         <v>22</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="30" t="s">
+      <c r="L12" s="31"/>
+      <c r="M12" s="29" t="s">
         <v>28</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="33" t="n">
+      <c r="P12" s="31"/>
+      <c r="Q12" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="26"/>
-      <c r="AC12" s="26"/>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="29"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="28"/>
+      <c r="AH12" s="28"/>
       <c r="AJ12" s="11" t="s">
         <v>15</v>
       </c>
@@ -1770,48 +1686,48 @@
       <c r="AL12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="45" t="s">
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="52" t="n">
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="53"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="53"/>
-      <c r="AB13" s="53"/>
-      <c r="AC13" s="53"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="53"/>
-      <c r="AG13" s="54"/>
-      <c r="AH13" s="53"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="48"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="48"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="48"/>
+      <c r="AE13" s="48"/>
+      <c r="AF13" s="48"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="48"/>
       <c r="AJ13" s="11"/>
       <c r="AK13" s="12"/>
       <c r="AL13" s="13" t="s">
@@ -1819,367 +1735,367 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="55"/>
+      <c r="B14" s="50"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="56" t="n">
+      <c r="A15" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="56" t="n">
+      <c r="B15" s="52"/>
+      <c r="C15" s="51" t="n">
         <f aca="false">A15+A17</f>
         <v>1</v>
       </c>
-      <c r="F15" s="56" t="n">
+      <c r="F15" s="51" t="n">
         <f aca="false">C15</f>
         <v>1</v>
       </c>
-      <c r="G15" s="57"/>
-      <c r="H15" s="56" t="n">
+      <c r="G15" s="52"/>
+      <c r="H15" s="51" t="n">
         <f aca="false">F15+F17</f>
         <v>3</v>
       </c>
-      <c r="K15" s="56" t="n">
+      <c r="K15" s="51" t="n">
         <f aca="false">H15</f>
         <v>3</v>
       </c>
-      <c r="L15" s="57"/>
-      <c r="M15" s="56" t="n">
+      <c r="L15" s="52"/>
+      <c r="M15" s="51" t="n">
         <f aca="false">K15+K17</f>
         <v>5</v>
       </c>
-      <c r="P15" s="56" t="n">
+      <c r="P15" s="51" t="n">
         <f aca="false">M15</f>
         <v>5</v>
       </c>
-      <c r="Q15" s="57"/>
-      <c r="R15" s="56" t="n">
+      <c r="Q15" s="52"/>
+      <c r="R15" s="51" t="n">
         <f aca="false">P15+P17</f>
         <v>8</v>
       </c>
-      <c r="U15" s="56" t="n">
+      <c r="U15" s="51" t="n">
         <f aca="false">MAX(R15,R21)</f>
         <v>8</v>
       </c>
-      <c r="V15" s="57"/>
-      <c r="W15" s="56" t="n">
+      <c r="V15" s="52"/>
+      <c r="W15" s="51" t="n">
         <f aca="false">U15+U17</f>
         <v>11</v>
       </c>
-      <c r="Z15" s="56" t="n">
+      <c r="Z15" s="51" t="n">
         <f aca="false">W15</f>
         <v>11</v>
       </c>
-      <c r="AA15" s="57"/>
-      <c r="AB15" s="56" t="n">
+      <c r="AA15" s="52"/>
+      <c r="AB15" s="51" t="n">
         <f aca="false">Z15+Z17</f>
         <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="F16" s="58" t="s">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="F16" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="K16" s="58" t="s">
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="K16" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="P16" s="58" t="s">
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="P16" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="U16" s="58" t="s">
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="U16" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="V16" s="58"/>
-      <c r="W16" s="58"/>
-      <c r="Z16" s="58" t="s">
+      <c r="V16" s="53"/>
+      <c r="W16" s="53"/>
+      <c r="Z16" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="AA16" s="58"/>
-      <c r="AB16" s="58"/>
+      <c r="AA16" s="53"/>
+      <c r="AB16" s="53"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="59" t="n">
+      <c r="A17" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="60" t="n">
+      <c r="B17" s="55" t="n">
         <f aca="false">C18-C15</f>
         <v>0</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="59" t="n">
+      <c r="C17" s="54"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="54" t="n">
         <f aca="false">Q5</f>
         <v>2</v>
       </c>
-      <c r="G17" s="60" t="n">
+      <c r="G17" s="55" t="n">
         <f aca="false">H18-H15</f>
         <v>0</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="59" t="n">
+      <c r="H17" s="54"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="54" t="n">
         <f aca="false">Q8</f>
         <v>2</v>
       </c>
-      <c r="L17" s="60" t="n">
+      <c r="L17" s="55" t="n">
         <f aca="false">M18-M15</f>
         <v>0</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="59" t="n">
+      <c r="M17" s="54"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="54" t="n">
         <f aca="false">Q9</f>
         <v>3</v>
       </c>
-      <c r="Q17" s="60" t="n">
+      <c r="Q17" s="55" t="n">
         <f aca="false">R18-R15</f>
         <v>0</v>
       </c>
-      <c r="R17" s="59"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="63"/>
-      <c r="U17" s="59" t="n">
+      <c r="R17" s="54"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="54" t="n">
         <f aca="false">Q12</f>
         <v>3</v>
       </c>
-      <c r="V17" s="60" t="n">
+      <c r="V17" s="55" t="n">
         <f aca="false">W18-W15</f>
         <v>0</v>
       </c>
-      <c r="W17" s="59"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="59" t="n">
+      <c r="W17" s="54"/>
+      <c r="X17" s="57"/>
+      <c r="Y17" s="57"/>
+      <c r="Z17" s="54" t="n">
         <f aca="false">Q13</f>
         <v>1</v>
       </c>
-      <c r="AA17" s="60" t="n">
+      <c r="AA17" s="55" t="n">
         <f aca="false">AB18-AB15</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="59"/>
+      <c r="AB17" s="54"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="64" t="n">
+      <c r="A18" s="59" t="n">
         <f aca="false">C18-A17</f>
         <v>0</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="64" t="n">
+      <c r="B18" s="50"/>
+      <c r="C18" s="59" t="n">
         <f aca="false">MIN(F18,F24,F30)</f>
         <v>1</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="F18" s="64" t="n">
+      <c r="D18" s="60"/>
+      <c r="F18" s="59" t="n">
         <f aca="false">H18-F17</f>
         <v>1</v>
       </c>
-      <c r="G18" s="55"/>
-      <c r="H18" s="64" t="n">
+      <c r="G18" s="50"/>
+      <c r="H18" s="59" t="n">
         <f aca="false">K18</f>
         <v>3</v>
       </c>
-      <c r="K18" s="64" t="n">
+      <c r="K18" s="59" t="n">
         <f aca="false">M18-K17</f>
         <v>3</v>
       </c>
-      <c r="L18" s="55"/>
-      <c r="M18" s="64" t="n">
+      <c r="L18" s="50"/>
+      <c r="M18" s="59" t="n">
         <f aca="false">P18</f>
         <v>5</v>
       </c>
-      <c r="P18" s="64" t="n">
+      <c r="P18" s="59" t="n">
         <f aca="false">R18-P17</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="64" t="n">
+      <c r="Q18" s="50"/>
+      <c r="R18" s="59" t="n">
         <f aca="false">U18</f>
         <v>8</v>
       </c>
-      <c r="T18" s="66"/>
-      <c r="U18" s="64" t="n">
+      <c r="T18" s="61"/>
+      <c r="U18" s="59" t="n">
         <f aca="false">W18-U17</f>
         <v>8</v>
       </c>
-      <c r="V18" s="55"/>
-      <c r="W18" s="64" t="n">
+      <c r="V18" s="50"/>
+      <c r="W18" s="59" t="n">
         <f aca="false">Z18</f>
         <v>11</v>
       </c>
-      <c r="Z18" s="64" t="n">
+      <c r="Z18" s="59" t="n">
         <f aca="false">AB18-Z17</f>
         <v>11</v>
       </c>
-      <c r="AA18" s="55"/>
-      <c r="AB18" s="64" t="n">
+      <c r="AA18" s="50"/>
+      <c r="AB18" s="59" t="n">
         <f aca="false">AB15</f>
         <v>12</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="65"/>
-      <c r="T19" s="66"/>
+      <c r="D19" s="60"/>
+      <c r="T19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="65"/>
-      <c r="T20" s="66"/>
+      <c r="D20" s="60"/>
+      <c r="T20" s="61"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="65"/>
-      <c r="F21" s="56" t="n">
+      <c r="D21" s="60"/>
+      <c r="F21" s="51" t="n">
         <f aca="false">C15</f>
         <v>1</v>
       </c>
-      <c r="G21" s="57"/>
-      <c r="H21" s="56" t="n">
+      <c r="G21" s="52"/>
+      <c r="H21" s="51" t="n">
         <f aca="false">F21+F23</f>
         <v>3</v>
       </c>
-      <c r="P21" s="56" t="n">
+      <c r="P21" s="51" t="n">
         <f aca="false">MAX(H21,H27)</f>
         <v>6</v>
       </c>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="56" t="n">
+      <c r="Q21" s="52"/>
+      <c r="R21" s="51" t="n">
         <f aca="false">P21+P23</f>
         <v>7</v>
       </c>
-      <c r="T21" s="66"/>
+      <c r="T21" s="61"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="65"/>
-      <c r="F22" s="58" t="s">
+      <c r="D22" s="60"/>
+      <c r="F22" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="P22" s="58" t="s">
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="P22" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="T22" s="66"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="T22" s="61"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="65"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="59" t="n">
+      <c r="D23" s="60"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="54" t="n">
         <f aca="false">Q6</f>
         <v>2</v>
       </c>
-      <c r="G23" s="60" t="n">
+      <c r="G23" s="55" t="n">
         <f aca="false">H24-H21</f>
         <v>4</v>
       </c>
-      <c r="H23" s="59"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="59" t="n">
+      <c r="H23" s="54"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="54" t="n">
         <f aca="false">Q11</f>
         <v>1</v>
       </c>
-      <c r="Q23" s="60" t="n">
+      <c r="Q23" s="55" t="n">
         <f aca="false">R24-R21</f>
         <v>1</v>
       </c>
-      <c r="R23" s="59"/>
-      <c r="S23" s="62"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="57"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="65"/>
-      <c r="F24" s="64" t="n">
+      <c r="D24" s="60"/>
+      <c r="F24" s="59" t="n">
         <f aca="false">H24-F23</f>
         <v>5</v>
       </c>
-      <c r="G24" s="55"/>
-      <c r="H24" s="64" t="n">
+      <c r="G24" s="50"/>
+      <c r="H24" s="59" t="n">
         <f aca="false">P24</f>
         <v>7</v>
       </c>
-      <c r="J24" s="66"/>
-      <c r="P24" s="64" t="n">
+      <c r="J24" s="61"/>
+      <c r="P24" s="59" t="n">
         <f aca="false">R24-P23</f>
         <v>7</v>
       </c>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="64" t="n">
+      <c r="Q24" s="50"/>
+      <c r="R24" s="59" t="n">
         <f aca="false">U18</f>
         <v>8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="65"/>
-      <c r="J25" s="66"/>
+      <c r="D25" s="60"/>
+      <c r="J25" s="61"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="65"/>
-      <c r="J26" s="66"/>
+      <c r="D26" s="60"/>
+      <c r="J26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="65"/>
-      <c r="F27" s="56" t="n">
+      <c r="D27" s="60"/>
+      <c r="F27" s="51" t="n">
         <f aca="false">C15</f>
         <v>1</v>
       </c>
-      <c r="G27" s="57"/>
-      <c r="H27" s="56" t="n">
+      <c r="G27" s="52"/>
+      <c r="H27" s="51" t="n">
         <f aca="false">F27+F29</f>
         <v>6</v>
       </c>
-      <c r="J27" s="66"/>
+      <c r="J27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="65"/>
-      <c r="F28" s="58" t="s">
+      <c r="D28" s="60"/>
+      <c r="F28" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="J28" s="66"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="J28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="62"/>
-      <c r="F29" s="59" t="n">
+      <c r="E29" s="57"/>
+      <c r="F29" s="54" t="n">
         <f aca="false">Q7</f>
         <v>5</v>
       </c>
-      <c r="G29" s="60" t="n">
+      <c r="G29" s="55" t="n">
         <f aca="false">H30-H27</f>
         <v>1</v>
       </c>
-      <c r="H29" s="59"/>
-      <c r="I29" s="62"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="57"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F30" s="64" t="n">
+      <c r="F30" s="59" t="n">
         <f aca="false">H30-F29</f>
         <v>2</v>
       </c>
-      <c r="G30" s="55"/>
-      <c r="H30" s="64" t="n">
+      <c r="G30" s="50"/>
+      <c r="H30" s="59" t="n">
         <f aca="false">P24</f>
         <v>7</v>
       </c>
@@ -2191,211 +2107,211 @@
       <c r="A33" s="0"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="67"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
+      <c r="A39" s="62"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="67"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="0" t="s">
         <v>30</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="L40" s="68"/>
+      <c r="L40" s="63"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="67"/>
-      <c r="B41" s="69" t="s">
+      <c r="A41" s="62"/>
+      <c r="B41" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="F41" s="70" t="s">
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="F41" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="L41" s="68"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="L41" s="63"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="67"/>
-      <c r="B42" s="71" t="s">
+      <c r="A42" s="62"/>
+      <c r="B42" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="71" t="s">
+      <c r="D42" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="L42" s="68"/>
+      <c r="L42" s="63"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="67"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="0" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="L43" s="68"/>
+      <c r="L43" s="63"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="67"/>
-      <c r="L44" s="68"/>
+      <c r="A44" s="62"/>
+      <c r="L44" s="63"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="67"/>
-      <c r="B45" s="73" t="s">
+      <c r="A45" s="62"/>
+      <c r="B45" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="74" t="s">
+      <c r="C45" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="74"/>
-      <c r="I45" s="74"/>
-      <c r="J45" s="74"/>
-      <c r="K45" s="74"/>
-      <c r="L45" s="68"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="63"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="67"/>
-      <c r="B46" s="73" t="s">
+      <c r="A46" s="62"/>
+      <c r="B46" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="74" t="s">
+      <c r="C46" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="74"/>
-      <c r="I46" s="74"/>
-      <c r="J46" s="74"/>
-      <c r="K46" s="74"/>
-      <c r="L46" s="68"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="63"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="67"/>
-      <c r="B47" s="73" t="s">
+      <c r="A47" s="62"/>
+      <c r="B47" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="74" t="s">
+      <c r="C47" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
-      <c r="I47" s="74"/>
-      <c r="J47" s="74"/>
-      <c r="K47" s="74"/>
-      <c r="L47" s="68"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="63"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="67"/>
-      <c r="B48" s="73" t="s">
+      <c r="A48" s="62"/>
+      <c r="B48" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="74" t="s">
+      <c r="C48" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="74"/>
-      <c r="I48" s="74"/>
-      <c r="J48" s="74"/>
-      <c r="K48" s="74"/>
-      <c r="L48" s="68"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="63"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="67"/>
-      <c r="B49" s="71" t="s">
+      <c r="A49" s="62"/>
+      <c r="B49" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="74" t="s">
+      <c r="C49" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="74"/>
-      <c r="K49" s="74"/>
-      <c r="L49" s="68"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="63"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="67"/>
-      <c r="B50" s="72" t="s">
+      <c r="A50" s="62"/>
+      <c r="B50" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="74" t="s">
+      <c r="C50" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="74"/>
-      <c r="I50" s="74"/>
-      <c r="J50" s="74"/>
-      <c r="K50" s="74"/>
-      <c r="L50" s="68"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="69"/>
+      <c r="L50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="67"/>
-      <c r="B51" s="75" t="s">
+      <c r="A51" s="62"/>
+      <c r="B51" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C51" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
-      <c r="L51" s="68"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="67"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="68"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
-      <c r="H52" s="68"/>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="68"/>
-      <c r="L52" s="68"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -2434,14 +2350,14 @@
     <mergeCell ref="C49:K49"/>
     <mergeCell ref="C50:K50"/>
   </mergeCells>
-  <conditionalFormatting sqref="AA17 V17 Q17 Q23 L17 G17 G23 G29 B17">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0</formula>
+  <conditionalFormatting sqref="Z2:AH10 Z12:AH13 R2:Y13 AA11:AH11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>IF(OR(WEEKDAY(R$2,2)=6,WEEKDAY(R$2,2)=7),1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AH10 Z12:AH13 R2:Y13 AA11:AH11">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>IF(OR(WEEKDAY(R$2,2)=6,WEEKDAY(R$2,2)=7),1,0)</formula>
+  <conditionalFormatting sqref="AA17 V17 Q17 Q23 L17 G17 G23 G29 B17">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
